--- a/result/收益率分析.xlsx
+++ b/result/收益率分析.xlsx
@@ -485,13 +485,13 @@
         <v>337</v>
       </c>
       <c r="C2" t="n">
-        <v>4.093115727002968</v>
+        <v>4.012433234421366</v>
       </c>
       <c r="D2" t="n">
-        <v>12.17613581634646</v>
+        <v>12.39553608744223</v>
       </c>
       <c r="E2" t="n">
-        <v>-59.35</v>
+        <v>-59.08</v>
       </c>
       <c r="F2" t="n">
         <v>6.22</v>

--- a/result/收益率分析.xlsx
+++ b/result/收益率分析.xlsx
@@ -516,22 +516,22 @@
         <v>235</v>
       </c>
       <c r="C3" t="n">
-        <v>3.754808510638298</v>
+        <v>5.88068085106383</v>
       </c>
       <c r="D3" t="n">
-        <v>20.64686454811731</v>
+        <v>25.84225973910466</v>
       </c>
       <c r="E3" t="n">
         <v>-19.77</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.845</v>
+        <v>-10.575</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.09</v>
+        <v>-3.08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.68</v>
+        <v>12.58</v>
       </c>
       <c r="I3" t="n">
         <v>196.3</v>

--- a/result/收益率分析.xlsx
+++ b/result/收益率分析.xlsx
@@ -485,13 +485,13 @@
         <v>337</v>
       </c>
       <c r="C2" t="n">
-        <v>4.012433234421366</v>
+        <v>3.95246290801187</v>
       </c>
       <c r="D2" t="n">
-        <v>12.39553608744223</v>
+        <v>12.71109250950045</v>
       </c>
       <c r="E2" t="n">
-        <v>-59.08</v>
+        <v>-61.2</v>
       </c>
       <c r="F2" t="n">
         <v>6.22</v>
@@ -500,7 +500,7 @@
         <v>6.73</v>
       </c>
       <c r="H2" t="n">
-        <v>7.64</v>
+        <v>7.65</v>
       </c>
       <c r="I2" t="n">
         <v>24.07</v>

--- a/result/收益率分析.xlsx
+++ b/result/收益率分析.xlsx
@@ -482,25 +482,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C2" t="n">
-        <v>3.95246290801187</v>
+        <v>3.803693181818182</v>
       </c>
       <c r="D2" t="n">
-        <v>12.71109250950045</v>
+        <v>13.23808300292018</v>
       </c>
       <c r="E2" t="n">
-        <v>-61.2</v>
+        <v>-62.26</v>
       </c>
       <c r="F2" t="n">
         <v>6.22</v>
       </c>
       <c r="G2" t="n">
-        <v>6.73</v>
+        <v>6.76</v>
       </c>
       <c r="H2" t="n">
-        <v>7.65</v>
+        <v>7.702500000000001</v>
       </c>
       <c r="I2" t="n">
         <v>24.07</v>
@@ -513,25 +513,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C3" t="n">
-        <v>5.88068085106383</v>
+        <v>5.926791666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>25.84225973910466</v>
+        <v>25.64120375159662</v>
       </c>
       <c r="E3" t="n">
         <v>-19.77</v>
       </c>
       <c r="F3" t="n">
-        <v>-10.575</v>
+        <v>-10.5725</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.08</v>
+        <v>-2.915</v>
       </c>
       <c r="H3" t="n">
-        <v>12.58</v>
+        <v>13.7625</v>
       </c>
       <c r="I3" t="n">
         <v>196.3</v>

--- a/result/收益率分析.xlsx
+++ b/result/收益率分析.xlsx
@@ -482,25 +482,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="C2" t="n">
-        <v>3.803693181818182</v>
+        <v>3.505263157894738</v>
       </c>
       <c r="D2" t="n">
-        <v>13.23808300292018</v>
+        <v>13.23048210228174</v>
       </c>
       <c r="E2" t="n">
         <v>-62.26</v>
       </c>
       <c r="F2" t="n">
-        <v>6.22</v>
+        <v>6.1675</v>
       </c>
       <c r="G2" t="n">
-        <v>6.76</v>
+        <v>6.72</v>
       </c>
       <c r="H2" t="n">
-        <v>7.702500000000001</v>
+        <v>7.6325</v>
       </c>
       <c r="I2" t="n">
         <v>24.07</v>
@@ -513,25 +513,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C3" t="n">
-        <v>5.926791666666667</v>
+        <v>5.401693548387096</v>
       </c>
       <c r="D3" t="n">
-        <v>25.64120375159662</v>
+        <v>25.45387762579816</v>
       </c>
       <c r="E3" t="n">
-        <v>-19.77</v>
+        <v>-28.63</v>
       </c>
       <c r="F3" t="n">
-        <v>-10.5725</v>
+        <v>-10.62</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.915</v>
+        <v>-3.42</v>
       </c>
       <c r="H3" t="n">
-        <v>13.7625</v>
+        <v>12.47</v>
       </c>
       <c r="I3" t="n">
         <v>196.3</v>
